--- a/DOSSIES_MULTIFORMATO/FUNTEA/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FUNTEA/dossie.xlsx
@@ -662,12 +662,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2016NE00301</t>
+          <t>2016NE00306</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9/2011</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5200.3</v>
+        <v>13605.76</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -685,19 +685,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5º TERMO ADITIVO AO CONTRATO Nº 009/2011</t>
+          <t>3º TERMO ADITIVO AO CONTRATO Nº008/2012.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2016NE00306</t>
+          <t>2016NE00301</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>9/2011</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13605.76</v>
+        <v>5200.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -715,19 +715,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3º TERMO ADITIVO AO CONTRATO Nº008/2012.</t>
+          <t>5º TERMO ADITIVO AO CONTRATO Nº 009/2011</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2018NE00502</t>
+          <t>2018NE00503</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>117.12</v>
+        <v>1302.98</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -745,19 +745,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste pelo índice IGPM de 8,91%.</t>
+          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP com reajuste pelo índice IGPM de 8,91%.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2018NE00503</t>
+          <t>2018NE00502</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1302.98</v>
+        <v>117.12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -775,21 +775,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP com reajuste pelo índice IGPM de 8,91%.</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste pelo índice IGPM de 8,91%.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2016NE00411</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6/2016</t>
-        </is>
-      </c>
+          <t>2016NE00410</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>30/11/2016</t>
@@ -805,7 +801,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Contrato nº 0006/2016 referente ao serviço de Acesso à Internet.</t>
+          <t>ANULAÇÃO TOTAL DA N.E. DE Nº00409/2016, PELO MOTIVO DA MODALIDADE ESTA INCORRETA.</t>
         </is>
       </c>
     </row>
@@ -842,10 +838,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2016NE00410</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>2016NE00411</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6/2016</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>30/11/2016</t>
@@ -861,19 +861,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA N.E. DE Nº00409/2016, PELO MOTIVO DA MODALIDADE ESTA INCORRETA.</t>
+          <t>Contrato nº 0006/2016 referente ao serviço de Acesso à Internet.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025NE0000615</t>
+          <t>2025NE0000613</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>186.13</v>
+        <v>4178.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025NE0000613</t>
+          <t>2025NE0000615</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4178.4</v>
+        <v>186.13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -951,19 +951,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 03.</t>
+          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024NE0000522</t>
+          <t>2024NE0000521</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>178.06</v>
+        <v>2236.92</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024NE0000521</t>
+          <t>2024NE0000522</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2236.92</v>
+        <v>178.06</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2022NE0000614</t>
+          <t>2022NE0000611</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>178.06</v>
+        <v>11.72</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 563/2022. Encerramento da execução orçamentária e financeira do exercício de 2022. Conforme decreto nº 46.621 publicado no Diário Oficial do Estado de 11/11/2022.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 459/2022. Encerramento da execução orçamentária e financeira do exercício de 2022. Conforme decreto nº 46.621 publicado no Diário Oficial do Estado de 11/11/2022.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2022NE0000613</t>
+          <t>2022NE0000612</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>173.56</v>
+        <v>370.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 533/2022. Encerramento da execução orçamentária e financeira do exercício de 2022. Conforme decreto nº 46.621 publicado no Diário Oficial do Estado de 11/11/2022.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 531/2022. Encerramento da execução orçamentária e financeira do exercício de 2022. Conforme decreto nº 46.621 publicado no Diário Oficial do Estado de 11/11/2022.</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2022NE0000612</t>
+          <t>2022NE0000613</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>370.3</v>
+        <v>173.56</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1227,14 +1227,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 531/2022. Encerramento da execução orçamentária e financeira do exercício de 2022. Conforme decreto nº 46.621 publicado no Diário Oficial do Estado de 11/11/2022.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 533/2022. Encerramento da execução orçamentária e financeira do exercício de 2022. Conforme decreto nº 46.621 publicado no Diário Oficial do Estado de 11/11/2022.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2022NE0000611</t>
+          <t>2022NE0000614</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.72</v>
+        <v>178.06</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 459/2022. Encerramento da execução orçamentária e financeira do exercício de 2022. Conforme decreto nº 46.621 publicado no Diário Oficial do Estado de 11/11/2022.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 563/2022. Encerramento da execução orçamentária e financeira do exercício de 2022. Conforme decreto nº 46.621 publicado no Diário Oficial do Estado de 11/11/2022.</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2019NE00529</t>
+          <t>2019NE00530</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3702.95</v>
+        <v>117.12</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados, conforme 3º aditivo ao contrato nº 006/2016.</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC, conforme 2º Aditivo ao Contrato nº 009</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2019NE00530</t>
+          <t>2019NE00529</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>117.12</v>
+        <v>3702.95</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC, conforme 2º Aditivo ao Contrato nº 009</t>
+          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados, conforme 3º aditivo ao contrato nº 006/2016.</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024NE0000407</t>
+          <t>2024NE0000406</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2236.92</v>
+        <v>3921.89</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024NE0000406</t>
+          <t>2024NE0000407</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3921.89</v>
+        <v>2236.92</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 02.</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1582,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024NE0000192</t>
+          <t>2024NE0000190</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4473.84</v>
+        <v>7843.78</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024NE0000190</t>
+          <t>2024NE0000192</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7843.78</v>
+        <v>4473.84</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 02.</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2018NE00586</t>
+          <t>2018NE00584</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1302.98</v>
+        <v>3702.95</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2018NE00584</t>
+          <t>2018NE00586</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3702.95</v>
+        <v>1302.98</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1840,12 +1840,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2020NE00227</t>
+          <t>2020NE00228</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10423.84</v>
+        <v>1054.08</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reforço da NE 011/2020 para Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP, conforme 3º Aditivo ao Contrato nº 007</t>
+          <t xml:space="preserve">Reforço da NE 0137/2020 para prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC, conforme </t>
         </is>
       </c>
     </row>
@@ -1900,12 +1900,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2020NE00228</t>
+          <t>2020NE00227</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1054.08</v>
+        <v>10423.84</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforço da NE 0137/2020 para prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC, conforme </t>
+          <t>Reforço da NE 011/2020 para Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP, conforme 3º Aditivo ao Contrato nº 007</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025NE0000211</t>
+          <t>2025NE0000210</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8356.799999999999</v>
+        <v>4676.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 03.</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025NE0000210</t>
+          <t>2025NE0000211</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4676.5</v>
+        <v>8356.799999999999</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025NE0000080</t>
+          <t>2025NE0000079</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>372.26</v>
+        <v>4676.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,19 +2069,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025NE0000079</t>
+          <t>2025NE0000080</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4676.5</v>
+        <v>372.26</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025NE0000472</t>
+          <t>2025NE0000474</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4178.4</v>
+        <v>186.13</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 03.</t>
+          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
         </is>
       </c>
     </row>
@@ -2248,12 +2248,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025NE0000474</t>
+          <t>2025NE0000472</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>186.13</v>
+        <v>4178.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -2308,12 +2308,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2017NE00215</t>
+          <t>2017NE00218</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5982</v>
+        <v>271.86</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2331,19 +2331,19 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Reforço da NE 0025/2017 referente ao Termo de Contrato nº 007/2016</t>
+          <t>Reforço da NE 0026/2017 referente ao 4º Termo Aditivo ao Contrato nº 008/12.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2017NE00218</t>
+          <t>2017NE00215</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>271.86</v>
+        <v>5982</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Reforço da NE 0026/2017 referente ao 4º Termo Aditivo ao Contrato nº 008/12.</t>
+          <t>Reforço da NE 0025/2017 referente ao Termo de Contrato nº 007/2016</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2024NE0000452</t>
+          <t>2024NE0000451</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>178.06</v>
+        <v>2236.92</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
@@ -2506,12 +2506,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2024NE0000451</t>
+          <t>2024NE0000452</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2236.92</v>
+        <v>178.06</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2529,19 +2529,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025NE0000326</t>
+          <t>2025NE0000325</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>372.26</v>
+        <v>8356.799999999999</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025NE0000325</t>
+          <t>2025NE0000326</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>8356.799999999999</v>
+        <v>372.26</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 03.</t>
+          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2020NE00392</t>
+          <t>2020NE00390</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3703.41</v>
+        <v>264.74</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2645,14 +2645,14 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>REF. AO QUARTO TERMO ADITIVO AO CONTRATO Nº0006/2016</t>
+          <t>PRODAM LICENÇA DE SOFTWARE VPN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020NE00389</t>
+          <t>2020NE00391</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1472.63</v>
+        <v>132.37</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2671,14 +2671,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA N.E. DE Nº367/2020, PELO MOTIVO DO MES DE NOVEMBRO ESTA COBERTO.</t>
+          <t>ANULAÇÃO PARCIAL DA N.E. DE Nº00390/2020, PELO MOTIVO DO MES DE NOVEMBRO/2020, ESTA COBERTO.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2020NE00391</t>
+          <t>2020NE00389</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>132.37</v>
+        <v>1472.63</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2697,19 +2697,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA N.E. DE Nº00390/2020, PELO MOTIVO DO MES DE NOVEMBRO/2020, ESTA COBERTO.</t>
+          <t>ANULAÇÃO PARCIAL DA N.E. DE Nº367/2020, PELO MOTIVO DO MES DE NOVEMBRO ESTA COBERTO.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2020NE00390</t>
+          <t>2020NE00392</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>264.74</v>
+        <v>3703.41</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PRODAM LICENÇA DE SOFTWARE VPN</t>
+          <t>REF. AO QUARTO TERMO ADITIVO AO CONTRATO Nº0006/2016</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2016NE00294</t>
+          <t>2016NE00293</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>9/2011</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1668.35</v>
+        <v>453.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2757,19 +2757,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>5º TERMO ADITIVO AO CONTRATO Nº 009/2011</t>
+          <t>3º TERMO ADITIVO AO CONTRATO Nº008/2012.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2016NE00293</t>
+          <t>2016NE00294</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>9/2011</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>453.1</v>
+        <v>1668.35</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2787,19 +2787,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>3º TERMO ADITIVO AO CONTRATO Nº008/2012.</t>
+          <t>5º TERMO ADITIVO AO CONTRATO Nº 009/2011</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2019NE00313</t>
+          <t>2019NE00312</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11108.85</v>
+        <v>351.36</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2817,19 +2817,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Reforço da NE 187/2019</t>
+          <t>Reforço da NE 00157/2019.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2019NE00312</t>
+          <t>2019NE00313</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>351.36</v>
+        <v>11108.85</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2847,19 +2847,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Reforço da NE 00157/2019.</t>
+          <t>Reforço da NE 187/2019</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2022NE0000229</t>
+          <t>2022NE0000227</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>14813.64</v>
+        <v>8400</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Prestação do Serviço de Rede, compreendendo o acesso gerenciado à Internet através da Rede de Governo.</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec.</t>
         </is>
       </c>
     </row>
@@ -2914,12 +2914,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2022NE0000227</t>
+          <t>2022NE0000229</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>8400</v>
+        <v>14813.64</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2937,19 +2937,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec.</t>
+          <t>Prestação do Serviço de Rede, compreendendo o acesso gerenciado à Internet através da Rede de Governo.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2021NE0000039</t>
+          <t>2021NE0000038</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>7406.82</v>
+        <v>2945.26</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>REF, A ACESSO A INTERNET</t>
+          <t>REF, AO CFPP</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2021NE0000038</t>
+          <t>2021NE0000039</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2945.26</v>
+        <v>7406.82</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3027,19 +3027,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>REF, AO CFPP</t>
+          <t>REF, A ACESSO A INTERNET</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2018NE00043</t>
+          <t>2018NE00042</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>20400</v>
+        <v>645.24</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados.</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC.</t>
         </is>
       </c>
     </row>
@@ -3094,12 +3094,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2018NE00042</t>
+          <t>2018NE00043</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>645.24</v>
+        <v>20400</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3117,14 +3117,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC.</t>
+          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2018NE00411</t>
+          <t>2018NE00410</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1196.38</v>
+        <v>6800</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE 0040/18 para regularização contábil devido a mudança da Natureza da Despesa.</t>
+          <t>Anulação total do saldo da NE 0043/18 para regularização contábil devido a mudança da Natureza da Despesa.</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2018NE00410</t>
+          <t>2018NE00411</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6800</v>
+        <v>1196.38</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3195,14 +3195,14 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE 0043/18 para regularização contábil devido a mudança da Natureza da Despesa.</t>
+          <t>Anulação total do saldo da NE 0040/18 para regularização contábil devido a mudança da Natureza da Despesa.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2015NE00499</t>
+          <t>2015NE00493</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>181.24</v>
+        <v>440.75</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2015NE00493</t>
+          <t>2015NE00499</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>440.75</v>
+        <v>181.24</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3392,12 +3392,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2015NE00190</t>
+          <t>2015NE00189</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>9/2011</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1238.17</v>
+        <v>181.24</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3415,19 +3415,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>REFORÇO DA N.E. DE Nº00013/2015.</t>
+          <t>REFORÇO DA N.E. DE Nº00012/2015.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2015NE00189</t>
+          <t>2015NE00190</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>9/2011</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>181.24</v>
+        <v>1238.17</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>REFORÇO DA N.E. DE Nº00012/2015.</t>
+          <t>REFORÇO DA N.E. DE Nº00013/2015.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2019NE00094</t>
+          <t>2019NE00095</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1302.98</v>
+        <v>3702.95</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO CAD FOLHA DE PAGAMENTO</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE ACESSO A INTERNETE</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3512,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2019NE00095</t>
+          <t>2019NE00094</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3702.95</v>
+        <v>1302.98</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3535,14 +3535,14 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE ACESSO A INTERNETE</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO CAD FOLHA DE PAGAMENTO</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2019NE00089</t>
+          <t>2019NE00091</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>135.04</v>
+        <v>3702.95</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE Nº0057/19 POR MOTIVO DA NATUREZA DA DESPESA ESTAR INCORRETA</t>
+          <t>ANULAÇÃO TOTAL DA NE Nº0059/19 POR MOTIVO DA NATUREZA DA DESPESA ESTAR INCORRETA</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2019NE00091</t>
+          <t>2019NE00089</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3702.95</v>
+        <v>135.04</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE Nº0059/19 POR MOTIVO DA NATUREZA DA DESPESA ESTAR INCORRETA</t>
+          <t>ANULAÇÃO TOTAL DA NE Nº0057/19 POR MOTIVO DA NATUREZA DA DESPESA ESTAR INCORRETA</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2018NE00568</t>
+          <t>2018NE00567</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>413.87</v>
+        <v>3162.72</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE 00453/18 para encerramento do exercício de 2018.</t>
+          <t>Anulação parcial do saldo da NE 00283/18 para encerramento do exercício de 2018.</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2018NE00567</t>
+          <t>2018NE00568</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3162.72</v>
+        <v>413.87</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3721,19 +3721,19 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Anulação parcial do saldo da NE 00283/18 para encerramento do exercício de 2018.</t>
+          <t>Anulação total do saldo da NE 00453/18 para encerramento do exercício de 2018.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2022NE0000368</t>
+          <t>2022NE0000369</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>3387.88</v>
+        <v>3703.41</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3751,19 +3751,19 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do Sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal no período de dezembro de 2021, conforme projeto básico e Nota fiscal. Com cobertura contratual (4º Ad</t>
+          <t>Prestação dos serviço de acesso a Rede mundial de internet por fibra óptica no período de dezembro de 2021, conforme projeto básico e Nota fiscal. Com cobertura contratual (4º Aditivo ao Contrato nº 0</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2022NE0000369</t>
+          <t>2022NE0000368</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>3703.41</v>
+        <v>3387.88</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3781,19 +3781,19 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Prestação dos serviço de acesso a Rede mundial de internet por fibra óptica no período de dezembro de 2021, conforme projeto básico e Nota fiscal. Com cobertura contratual (4º Aditivo ao Contrato nº 0</t>
+          <t>Prestação dos serviços de execução do Sistema PRODAMRH - Cadastro e Folha de Pagamento de Pessoal no período de dezembro de 2021, conforme projeto básico e Nota fiscal. Com cobertura contratual (4º Ad</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2019NE00059</t>
+          <t>2019NE00057</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3702.95</v>
+        <v>135.04</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>REFERENTE AO PAGAMENTO DA NFSe, Nº 5741/2018</t>
+          <t>REFERENTE AO PAGAMENTO DA NFSe, Nº 5404 E 5662/2018</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2019NE00057</t>
+          <t>2019NE00059</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>135.04</v>
+        <v>3702.95</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>REFERENTE AO PAGAMENTO DA NFSe, Nº 5404 E 5662/2018</t>
+          <t>REFERENTE AO PAGAMENTO DA NFSe, Nº 5741/2018</t>
         </is>
       </c>
     </row>
@@ -3934,12 +3934,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2023NE0000306</t>
+          <t>2023NE0000305</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>7843.78</v>
+        <v>356.12</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3957,19 +3957,19 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. Com reajuste de 5,90% com base no IGPM acumulado do período, confo</t>
+          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2023NE0000305</t>
+          <t>2023NE0000306</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>356.12</v>
+        <v>7843.78</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN.</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. Com reajuste de 5,90% com base no IGPM acumulado do período, confo</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4020,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2021NE0000221</t>
+          <t>2021NE0000220</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>8835.780000000001</v>
+        <v>794.22</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4043,24 +4043,28 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Reforço da NE nº 192/2021 para Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP.</t>
+          <t>Reforço da NE 191/2021 para Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2021NE0000219</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>2021NE0000222</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>6/2016</t>
+        </is>
+      </c>
       <c r="C121" t="inlineStr">
         <is>
           <t>15/07/2021</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>350.48</v>
+        <v>22220.46</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4069,28 +4073,24 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE 0038/2021.</t>
+          <t>Reforço da NE nº 193/2021 para Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2021NE0000222</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>6/2016</t>
-        </is>
-      </c>
+          <t>2021NE0000219</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
           <t>15/07/2021</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>22220.46</v>
+        <v>350.48</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4099,19 +4099,19 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Reforço da NE nº 193/2021 para Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo.</t>
+          <t>Anulação total do saldo da NE 0038/2021.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2021NE0000220</t>
+          <t>2021NE0000221</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>794.22</v>
+        <v>8835.780000000001</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4129,19 +4129,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Reforço da NE 191/2021 para Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC.</t>
+          <t>Reforço da NE nº 192/2021 para Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2018NE00131</t>
+          <t>2018NE00130</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>967.86</v>
+        <v>10767.42</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC conforme contrato nº 009/2017</t>
+          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP, conforme 1º Aditivo ao Contrato nº 007/2016</t>
         </is>
       </c>
     </row>
@@ -4196,12 +4196,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2018NE00130</t>
+          <t>2018NE00131</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10767.42</v>
+        <v>967.86</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP, conforme 1º Aditivo ao Contrato nº 007/2016</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC conforme contrato nº 009/2017</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2024NE0000094</t>
+          <t>2024NE0000093</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4473.84</v>
+        <v>356.12</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4279,19 +4279,19 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2024NE0000093</t>
+          <t>2024NE0000094</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>356.12</v>
+        <v>4473.84</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4309,19 +4309,19 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2018NE00451</t>
+          <t>2018NE00453</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>215.08</v>
+        <v>1158.26</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4339,19 +4339,19 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC, conf. Termo de Contrato nº 009/17.</t>
+          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP, conf. 1º Termo Aditivo ao Contrato 007/2016.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2018NE00453</t>
+          <t>2018NE00451</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1158.26</v>
+        <v>215.08</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP, conf. 1º Termo Aditivo ao Contrato 007/2016.</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC, conf. Termo de Contrato nº 009/17.</t>
         </is>
       </c>
     </row>
@@ -4436,12 +4436,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2022NE0000533</t>
+          <t>2022NE0000531</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>173.56</v>
+        <v>11110.23</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste de 31,12% no valor mensal,</t>
+          <t>Prestação do Serviço de Rede, compreendendo o acesso gerenciado à Internet através da Rede de Governo.</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2022NE0000531</t>
+          <t>2022NE0000533</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11110.23</v>
+        <v>173.56</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Prestação do Serviço de Rede, compreendendo o acesso gerenciado à Internet através da Rede de Governo.</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste de 31,12% no valor mensal,</t>
         </is>
       </c>
     </row>
@@ -4552,12 +4552,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2023NE0000511</t>
+          <t>2023NE0000510</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>6710.76</v>
+        <v>15687.56</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4575,19 +4575,19 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. Com reajuste de 5,90% com base no IGPM acumulado do período, confo</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2023NE0000510</t>
+          <t>2023NE0000511</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>15687.56</v>
+        <v>6710.76</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4605,19 +4605,19 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. Com reajuste de 5,90% com base no IGPM acumulado do período, confo</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2019NE00162</t>
+          <t>2019NE00161</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3908.94</v>
+        <v>11108.85</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4635,19 +4635,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP com reajuste pelo índice IGPM de 8,91%.</t>
+          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados com aplicação do reajuste pelo índice IGPM acumulado de 8,</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2019NE00157</t>
+          <t>2019NE00154</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>2/2018</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>351.36</v>
+        <v>4744.08</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4665,19 +4665,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste pelo índice IGPM de 8,91%.</t>
+          <t>Prestação dos serviços de licença de uso de sistema informação, compreendendo a disponibilização de Gestor de Conteúdo web, para publicação de informações, notícias, vídeos e imagens via website.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2019NE00154</t>
+          <t>2019NE00157</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2/2018</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>4744.08</v>
+        <v>351.36</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4695,19 +4695,19 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de licença de uso de sistema informação, compreendendo a disponibilização de Gestor de Conteúdo web, para publicação de informações, notícias, vídeos e imagens via website.</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste pelo índice IGPM de 8,91%.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2019NE00161</t>
+          <t>2019NE00162</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11108.85</v>
+        <v>3908.94</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados com aplicação do reajuste pelo índice IGPM acumulado de 8,</t>
+          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP com reajuste pelo índice IGPM de 8,91%.</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2023NE0000069</t>
+          <t>2023NE0000067</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>8947.68</v>
+        <v>712.24</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4845,19 +4845,19 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2023NE0000067</t>
+          <t>2023NE0000069</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>712.24</v>
+        <v>8947.68</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN.</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
@@ -4960,12 +4960,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2019NE00467</t>
+          <t>2019NE00465</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>234.24</v>
+        <v>7405.9</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste pelo índice IGPM de 8,91%.</t>
+          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados com aplicação do reajuste pelo índice IGPM acumulado de 8,</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5020,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2019NE00465</t>
+          <t>2019NE00467</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>7405.9</v>
+        <v>234.24</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados com aplicação do reajuste pelo índice IGPM acumulado de 8,</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste pelo índice IGPM de 8,91%.</t>
         </is>
       </c>
     </row>
@@ -5140,12 +5140,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026NE0000036</t>
+          <t>2026NE0000037</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>751.36</v>
+        <v>9439.09</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5163,19 +5163,19 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026NE0000037</t>
+          <t>2026NE0000036</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>9439.09</v>
+        <v>751.36</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5193,19 +5193,19 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2015NE00360</t>
+          <t>2015NE00361</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>9/2011</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5214,7 +5214,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>5200.3</v>
+        <v>543.72</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5223,19 +5223,19 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>4º TERMO ADITIVO AO CONTRATO Nº 009/2011</t>
+          <t>2º TERMO ADITIVO AO CONTRATO Nº 008/2015</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2015NE00361</t>
+          <t>2015NE00360</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>9/2011</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>543.72</v>
+        <v>5200.3</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO CONTRATO Nº 008/2015</t>
+          <t>4º TERMO ADITIVO AO CONTRATO Nº 009/2011</t>
         </is>
       </c>
     </row>
@@ -5342,12 +5342,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2021NE0000424</t>
+          <t>2021NE0000423</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2945.26</v>
+        <v>3703.41</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5365,19 +5365,19 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP, com acrescimo de 13,02% no valor mensal conforme DP 511 de 16/09/2</t>
+          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados e com acréscimo de 0,0124% no valor mensal, conforme DP 52</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2021NE0000423</t>
+          <t>2021NE0000424</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3703.41</v>
+        <v>2945.26</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados e com acréscimo de 0,0124% no valor mensal, conforme DP 52</t>
+          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP, com acrescimo de 13,02% no valor mensal conforme DP 511 de 16/09/2</t>
         </is>
       </c>
     </row>
@@ -5458,12 +5458,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2015NE00013</t>
+          <t>2015NE00012</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>9/2011</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>3714.51</v>
+        <v>271.86</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5488,12 +5488,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2015NE00012</t>
+          <t>2015NE00013</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>9/2011</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>271.86</v>
+        <v>3714.51</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5518,12 +5518,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2024NE0000297</t>
+          <t>2024NE0000299</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>7843.78</v>
+        <v>4473.84</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 02.</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
@@ -5578,12 +5578,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2024NE0000299</t>
+          <t>2024NE0000297</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>4473.84</v>
+        <v>7843.78</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2016NE00027</t>
+          <t>2016NE00028</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>5200.3</v>
+        <v>6240.36</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>5º TERMO ADITIVO AO CONTRATO Nº 009/2011.</t>
+          <t>5º TERMO ADITIVO AO CONTRATO Nº 009/2011</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2016NE00028</t>
+          <t>2016NE00027</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5712,7 +5712,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>6240.36</v>
+        <v>5200.3</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5721,19 +5721,19 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>5º TERMO ADITIVO AO CONTRATO Nº 009/2011</t>
+          <t>5º TERMO ADITIVO AO CONTRATO Nº 009/2011.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025NE0000689</t>
+          <t>2025NE0000688</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>186.13</v>
+        <v>4178.4</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5751,19 +5751,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025NE0000688</t>
+          <t>2025NE0000689</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4178.4</v>
+        <v>186.13</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5781,19 +5781,19 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 03.</t>
+          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025NE0000556</t>
+          <t>2025NE0000554</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1/2023</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>186.13</v>
+        <v>4178.4</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -5848,12 +5848,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025NE0000554</t>
+          <t>2025NE0000556</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4178.4</v>
+        <v>186.13</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5871,19 +5871,19 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 03.</t>
+          <t>Prestação dos serviços de rede de Internet, compreendendo a disponibilização de 1 (um) acesso aos sistemas hospedados no Data Center do Estado do Amazonas por meio do Virtual Private Network - VPN. TC</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2021NE0000191</t>
+          <t>2021NE0000193</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>264.74</v>
+        <v>7406.82</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste de 13,02% no valor mensal,</t>
+          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados e com acréscimo de 0,0124% no valor mensal, conforme DP 52</t>
         </is>
       </c>
     </row>
@@ -5938,12 +5938,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2021NE0000193</t>
+          <t>2021NE0000191</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>7406.82</v>
+        <v>264.74</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5961,14 +5961,14 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados e com acréscimo de 0,0124% no valor mensal, conforme DP 52</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste de 13,02% no valor mensal,</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2016NE00057</t>
+          <t>2016NE00056</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1312.66</v>
+        <v>705.39</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5991,14 +5991,14 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DÍVIDA DE EXERCÍCIOS ANTERIORES, RD Nº2016RD00008</t>
+          <t>RECONHECIMENTO DA DÍVIDA DE EXERCÍCIOS ANTERIORES, RD Nº2016RD00016</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2016NE00056</t>
+          <t>2016NE00057</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>705.39</v>
+        <v>1312.66</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6021,19 +6021,19 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DÍVIDA DE EXERCÍCIOS ANTERIORES, RD Nº2016RD00016</t>
+          <t>RECONHECIMENTO DA DÍVIDA DE EXERCÍCIOS ANTERIORES, RD Nº2016RD00008</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025NE0000005</t>
+          <t>2025NE0000019</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>7843.78</v>
+        <v>4676.53</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 02.</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025NE0000019</t>
+          <t>2025NE0000005</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>4676.53</v>
+        <v>7843.78</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6111,19 +6111,19 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. TC: 0006/2022 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2024NE0000006</t>
+          <t>2024NE0000003</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>4473.84</v>
+        <v>7843.78</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6141,19 +6141,19 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
+          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. Com reajuste de 5,90% com base no IGPM acumulado do período, confo</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2024NE0000003</t>
+          <t>2024NE0000006</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>6/2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>7843.78</v>
+        <v>4473.84</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Contratação para a Prestação do Serviço de Rede de internet, compreendendo o acesso gerenciado à Internet através da Rede de Governo. Com reajuste de 5,90% com base no IGPM acumulado do período, confo</t>
+          <t>Prestação dos serviços de execução do sistema PRODAM RH para o cadastro da folha de pagamento de pessoal (CFPP) da Funtec, com reajuste de 6,52% no valor mensal. Conforme Cláusula Décima Primeira e DI</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2020NE00012</t>
+          <t>2020NE00010</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>234.24</v>
+        <v>3702.95</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC.</t>
+          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados.</t>
         </is>
       </c>
     </row>
@@ -6268,12 +6268,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2020NE00010</t>
+          <t>2020NE00012</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>3702.95</v>
+        <v>234.24</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6291,19 +6291,19 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados.</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2019NE00007</t>
+          <t>2019NE00011</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>2/2018</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>3908.94</v>
+        <v>4744.08</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6321,19 +6321,19 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP com reajuste pelo índice IGPM de 8,91%.</t>
+          <t>Prestação dos serviços de licença de uso de sistema informação, compreendendo a disponibilização de Gestor de Conteúdo web, para publicação de informações, notícias, vídeos e imagens via website.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2019NE00008</t>
+          <t>2019NE00006</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>351.36</v>
+        <v>11108.85</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6351,19 +6351,19 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste pelo índice IGPM de 8,91%.</t>
+          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados com aplicação do reajuste pelo índice IGPM acumulado de 8,</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2019NE00006</t>
+          <t>2019NE00008</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>11108.85</v>
+        <v>351.36</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6381,19 +6381,19 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados com aplicação do reajuste pelo índice IGPM acumulado de 8,</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste pelo índice IGPM de 8,91%.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2019NE00011</t>
+          <t>2019NE00007</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2/2018</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6402,7 +6402,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>4744.08</v>
+        <v>3908.94</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6411,19 +6411,19 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Prestação dos serviços de licença de uso de sistema informação, compreendendo a disponibilização de Gestor de Conteúdo web, para publicação de informações, notícias, vídeos e imagens via website.</t>
+          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP com reajuste pelo índice IGPM de 8,91%.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2017NE00026</t>
+          <t>2017NE00025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>362.48</v>
+        <v>4785.52</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>4º TERMO ADITIVO AO CONTRATO Nº008/2012.</t>
+          <t>TERMO DE CONTRATO Nº 007/2016.</t>
         </is>
       </c>
     </row>
@@ -6478,12 +6478,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2017NE00025</t>
+          <t>2017NE00026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>4785.52</v>
+        <v>362.48</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>TERMO DE CONTRATO Nº 007/2016.</t>
+          <t>4º TERMO ADITIVO AO CONTRATO Nº008/2012.</t>
         </is>
       </c>
     </row>
@@ -6538,12 +6538,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2017NE00391</t>
+          <t>2017NE00395</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6552,7 +6552,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>421.5</v>
+        <v>107.54</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6561,19 +6561,19 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP, conforme Termo de Contrato nº 007/2016 (Reforço da NE 0025/17.</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2017NE00392</t>
+          <t>2017NE00394</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>6/2016</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1196.38</v>
+        <v>3400</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6591,19 +6591,19 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP.</t>
+          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2017NE00394</t>
+          <t>2017NE00392</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>6/2016</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>3400</v>
+        <v>1196.38</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6621,19 +6621,19 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados.</t>
+          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2017NE00395</t>
+          <t>2017NE00391</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>107.54</v>
+        <v>421.5</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6651,28 +6651,24 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC.</t>
+          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP, conforme Termo de Contrato nº 007/2016 (Reforço da NE 0025/17.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2016NE00416</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>7/2016</t>
-        </is>
-      </c>
+          <t>2016NE00415</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
           <t>01/12/2016</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1196.38</v>
+        <v>1743.87</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -6681,24 +6677,28 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>TERMO DE CONTRATO Nº 007/2016.</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DA NE 0027/2016 PARA REGULARIZAÇÃO CONTÁBIL.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2016NE00415</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr"/>
+          <t>2016NE00416</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>7/2016</t>
+        </is>
+      </c>
       <c r="C210" t="inlineStr">
         <is>
           <t>01/12/2016</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1743.87</v>
+        <v>1196.38</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6707,14 +6707,14 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DA NE 0027/2016 PARA REGULARIZAÇÃO CONTÁBIL.</t>
+          <t>TERMO DE CONTRATO Nº 007/2016.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2015NE00435</t>
+          <t>2015NE00434</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>90.62</v>
+        <v>181.24</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -6737,14 +6737,14 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>3º TERMO ADITIVO AO CONTRATO Nº 008/2012</t>
+          <t>2º TERMO ADITIVO AO CONTRATO Nº 008/2015</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2015NE00434</t>
+          <t>2015NE00435</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>181.24</v>
+        <v>90.62</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6767,14 +6767,14 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO CONTRATO Nº 008/2015</t>
+          <t>3º TERMO ADITIVO AO CONTRATO Nº 008/2012</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2016NE00367</t>
+          <t>2016NE00360</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>4530.48</v>
+        <v>889.13</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE 028/2016 para regularização contábil.</t>
+          <t>Anulação total do saldo da NE 0027/2016 para regularização contábil.</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2016NE00360</t>
+          <t>2016NE00367</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>889.13</v>
+        <v>4530.48</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6845,28 +6845,24 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE 0027/2016 para regularização contábil.</t>
+          <t>Anulação total do saldo da NE 028/2016 para regularização contábil.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2021NE0000322</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>9/2017</t>
-        </is>
-      </c>
+          <t>2021NE0000319</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
         <is>
           <t>01/09/2021</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>397.11</v>
+        <v>264.74</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6875,28 +6871,24 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste de 13,02% no valor mensal,</t>
+          <t>ANULAÇÃO TOTAL DA NE Nº 191/2021, POR MOTIVO DE ERRO NO CRONOGRAMA DE DESEMBOLSO</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2021NE0000320</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>6/2016</t>
-        </is>
-      </c>
+          <t>2021NE0000317</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
         <is>
           <t>01/09/2021</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>11110.23</v>
+        <v>7538.64</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6905,28 +6897,24 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados e com acréscimo de 0,0124% no valor mensal, conforme DP 52</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DA NE Nº 0192/2021.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2021NE0000321</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>7/2016</t>
-        </is>
-      </c>
+          <t>2021NE0000318</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
         <is>
           <t>01/09/2021</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>4417.89</v>
+        <v>11110.23</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6935,24 +6923,28 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP, com acrescimo de 13,02% no valor mensal conforme DP 511 de 16/09/2</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DA NE Nº 0193/2021, POR MOTIVO DE INCORREÇÃO NO CRONOGRAMA DE DESEMBOLSO.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2021NE0000318</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr"/>
+          <t>2021NE0000321</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>7/2016</t>
+        </is>
+      </c>
       <c r="C219" t="inlineStr">
         <is>
           <t>01/09/2021</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>11110.23</v>
+        <v>4417.89</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6961,24 +6953,28 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DA NE Nº 0193/2021, POR MOTIVO DE INCORREÇÃO NO CRONOGRAMA DE DESEMBOLSO.</t>
+          <t>Prestação de serviços de execução de sistemas PRODAM-RH, para manter o cadastro de servidores e folha de pagamento de pessoal - CFPP, com acrescimo de 13,02% no valor mensal conforme DP 511 de 16/09/2</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2021NE0000317</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr"/>
+          <t>2021NE0000320</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>6/2016</t>
+        </is>
+      </c>
       <c r="C220" t="inlineStr">
         <is>
           <t>01/09/2021</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>7538.64</v>
+        <v>11110.23</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6987,24 +6983,28 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DA NE Nº 0192/2021.</t>
+          <t>Prestação de serviços de acesso à rede de internet, compreendendo o fornecimento do serviço via Rede de Governo, através de circuito de dados e com acréscimo de 0,0124% no valor mensal, conforme DP 52</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2021NE0000319</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr"/>
+          <t>2021NE0000322</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>9/2017</t>
+        </is>
+      </c>
       <c r="C221" t="inlineStr">
         <is>
           <t>01/09/2021</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>264.74</v>
+        <v>397.11</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE Nº 191/2021, POR MOTIVO DE ERRO NO CRONOGRAMA DE DESEMBOLSO</t>
+          <t>Prestação de serviços de rede, compreendendo a disponibilização de 1 (um) acesso ao VPN (Virtual Private Network), para acesso aos sistema utilizado pela FUNTEC com reajuste de 13,02% no valor mensal,</t>
         </is>
       </c>
     </row>
@@ -7046,12 +7046,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2018NE00123</t>
+          <t>2018NE00120</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>9/2017</t>
+          <t>7/2016</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>430.16</v>
+        <v>5981.9</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE 0042/2018 para mudança no elemento de despesa conforme Orientação Técnica nº12/2018-GINS.</t>
+          <t>Anulação total do saldo da NE 0040/2018 para mudança no elemento de despesa conforme Orientação Técnica nº12/2018-GINS.</t>
         </is>
       </c>
     </row>
@@ -7106,12 +7106,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2018NE00120</t>
+          <t>2018NE00123</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>7/2016</t>
+          <t>9/2017</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>5981.9</v>
+        <v>430.16</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE 0040/2018 para mudança no elemento de despesa conforme Orientação Técnica nº12/2018-GINS.</t>
+          <t>Anulação total do saldo da NE 0042/2018 para mudança no elemento de despesa conforme Orientação Técnica nº12/2018-GINS.</t>
         </is>
       </c>
     </row>
